--- a/events/LaSeu_2019_WCH/LaSeu_2019_WCH_start.xlsx
+++ b/events/LaSeu_2019_WCH/LaSeu_2019_WCH_start.xlsx
@@ -56034,6 +56034,11 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
+      <c r="X915" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
       <c r="Y915" t="inlineStr">
         <is>
           <t>35079</t>
@@ -56165,6 +56170,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X917" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y917" t="inlineStr">
         <is>
           <t>35061</t>
@@ -56316,6 +56326,11 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
+      <c r="X919" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
       <c r="Y919" t="inlineStr">
         <is>
           <t>35079</t>
@@ -56777,6 +56792,11 @@
       <c r="S925" t="inlineStr">
         <is>
           <t>JANE Jakub</t>
+        </is>
+      </c>
+      <c r="X925" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
       <c r="Y925" t="inlineStr">
